--- a/SGC-CKN/Excel/a435dac0-1d9d-4c6f-8c9c-91294ed9e0b8_Lô_CT-02_P7-13_D800_24-03-2024.xlsx
+++ b/SGC-CKN/Excel/a435dac0-1d9d-4c6f-8c9c-91294ed9e0b8_Lô_CT-02_P7-13_D800_24-03-2024.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>15:22 24/03/2024</t>
+    <t>00:20 24/03/2024</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -119,7 +119,7 @@
 23/03/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">14:45
+    <t xml:space="preserve">14:31
 23/03/2024</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">14:46
+    <t xml:space="preserve">14:32
 23/03/2024</t>
   </si>
   <si>
@@ -161,7 +161,7 @@
 23/03/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">17:58
+    <t xml:space="preserve">17:48
 23/03/2024</t>
   </si>
   <si>
@@ -171,7 +171,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:59
+    <t xml:space="preserve">17:49
 23/03/2024</t>
   </si>
   <si>
@@ -210,7 +210,7 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">21:56
+    <t xml:space="preserve">21:36
 23/03/2024</t>
   </si>
   <si>
@@ -228,7 +228,7 @@
 23/03/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">06:18
+    <t xml:space="preserve">00:20
 24/03/2024</t>
   </si>
   <si>
@@ -266,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -349,12 +349,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -365,7 +359,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,11 +439,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -545,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -655,16 +644,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.88</v>
@@ -1259,10 +1245,10 @@
         <v>0.37</v>
       </c>
       <c r="I11" s="5">
-        <v>5.17</v>
+        <v>6.88</v>
       </c>
       <c r="J11" s="8">
-        <v>14.1</v>
+        <v>18.76</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1288,16 +1274,16 @@
         <v>-6.88</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.15</v>
+        <v>-9.03</v>
       </c>
       <c r="H12" s="9">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="I12" s="9">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="J12" s="8">
-        <v>6.19</v>
+        <v>16.12</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1320,19 +1306,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.15</v>
+        <v>-9.03</v>
       </c>
       <c r="G13" s="12">
         <v>-17.23</v>
       </c>
       <c r="H13" s="12">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="12">
-        <v>8.08</v>
+        <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>7.58</v>
+        <v>6.31</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1396,13 +1382,13 @@
         <v>-25.6</v>
       </c>
       <c r="H15" s="19">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="I15" s="19">
         <v>4.1</v>
       </c>
       <c r="J15" s="18">
-        <v>3.67</v>
+        <v>4.32</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1431,13 +1417,13 @@
         <v>-35.7</v>
       </c>
       <c r="H16" s="22">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="I16" s="22">
         <v>10.1</v>
       </c>
       <c r="J16" s="18">
-        <v>4.73</v>
+        <v>4.39</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1463,16 +1449,16 @@
         <v>-35.7</v>
       </c>
       <c r="G17" s="25">
-        <v>-37.47</v>
+        <v>-37.97</v>
       </c>
       <c r="H17" s="25">
         <v>0.53</v>
       </c>
       <c r="I17" s="25">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="J17" s="18">
-        <v>3.32</v>
+        <v>4.26</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1495,7 +1481,7 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-37.47</v>
+        <v>-37.97</v>
       </c>
       <c r="G18" s="28">
         <v>-39.5</v>
@@ -1504,10 +1490,10 @@
         <v>0.73</v>
       </c>
       <c r="I18" s="28">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="J18" s="18">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1536,13 +1522,13 @@
         <v>-44.15</v>
       </c>
       <c r="H19" s="31">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="I19" s="31">
         <v>4.65</v>
       </c>
       <c r="J19" s="18">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1568,35 +1554,35 @@
         <v>-44.15</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.18</v>
+        <v>-45.11</v>
       </c>
       <c r="H20" s="34">
-        <v>6.43</v>
+        <v>0.47</v>
       </c>
       <c r="I20" s="34">
-        <v>1.03</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.16</v>
+        <v>0.96</v>
+      </c>
+      <c r="J20" s="18">
+        <v>2.06</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1732,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.88</v>
@@ -1741,10 +1727,10 @@
         <v>0.37</v>
       </c>
       <c r="H2" s="5">
-        <v>5.17</v>
+        <v>6.88</v>
       </c>
       <c r="I2" s="8">
-        <v>14.1</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1764,16 +1750,16 @@
         <v>-6.88</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.15</v>
+        <v>-9.03</v>
       </c>
       <c r="G3" s="9">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="H3" s="9">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="I3" s="8">
-        <v>6.19</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1790,19 +1776,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.15</v>
+        <v>-9.03</v>
       </c>
       <c r="F4" s="12">
         <v>-17.23</v>
       </c>
       <c r="G4" s="12">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="H4" s="12">
-        <v>8.08</v>
+        <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>7.58</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1854,13 +1840,13 @@
         <v>-25.6</v>
       </c>
       <c r="G6" s="19">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H6" s="19">
         <v>4.1</v>
       </c>
       <c r="I6" s="18">
-        <v>3.67</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1883,13 +1869,13 @@
         <v>-35.7</v>
       </c>
       <c r="G7" s="22">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="H7" s="22">
         <v>10.1</v>
       </c>
       <c r="I7" s="18">
-        <v>4.73</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1909,16 +1895,16 @@
         <v>-35.7</v>
       </c>
       <c r="F8" s="25">
-        <v>-37.47</v>
+        <v>-37.97</v>
       </c>
       <c r="G8" s="25">
         <v>0.53</v>
       </c>
       <c r="H8" s="25">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="I8" s="18">
-        <v>3.32</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1935,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.47</v>
+        <v>-37.97</v>
       </c>
       <c r="F9" s="28">
         <v>-39.5</v>
@@ -1944,10 +1930,10 @@
         <v>0.73</v>
       </c>
       <c r="H9" s="28">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="18">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1970,13 +1956,13 @@
         <v>-44.15</v>
       </c>
       <c r="G10" s="31">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="H10" s="31">
         <v>4.65</v>
       </c>
       <c r="I10" s="18">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1996,45 +1982,45 @@
         <v>-44.15</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.18</v>
+        <v>-45.11</v>
       </c>
       <c r="G11" s="34">
-        <v>6.43</v>
+        <v>0.47</v>
       </c>
       <c r="H11" s="34">
-        <v>1.03</v>
-      </c>
-      <c r="I11" s="37">
-        <v>0.16</v>
+        <v>0.96</v>
+      </c>
+      <c r="I11" s="18">
+        <v>2.06</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-1.71</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-45.18</v>
-      </c>
-      <c r="G12" s="40">
-        <v>15.65</v>
-      </c>
-      <c r="H12" s="40">
-        <v>43.47</v>
-      </c>
-      <c r="I12" s="40">
-        <v>2.78</v>
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
+        <v>-45.11</v>
+      </c>
+      <c r="G12" s="39">
+        <v>10.02</v>
+      </c>
+      <c r="H12" s="39">
+        <v>45.11</v>
+      </c>
+      <c r="I12" s="39">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/a435dac0-1d9d-4c6f-8c9c-91294ed9e0b8_Lô_CT-02_P7-13_D800_24-03-2024.xlsx
+++ b/SGC-CKN/Excel/a435dac0-1d9d-4c6f-8c9c-91294ed9e0b8_Lô_CT-02_P7-13_D800_24-03-2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>14:00 23/03/2024</t>
+    <t>14:00 23/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>00:20 24/03/2024</t>
+    <t>00:20 24/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -92,144 +92,141 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:22
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:23
+23/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:31
+23/03/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:32
+23/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:50
+23/03/2026</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:51
+23/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:50
+23/03/2026</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:23
-23/03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:31
-23/03/2024</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:32
-23/03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:50
-23/03/2024</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:51
-23/03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:50
-23/03/2024</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi san, có chỗ là cát hạt nhỏ bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">16:51
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:48
-23/03/2024</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+23/03/2026</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:49
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:07
-23/03/2024</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+23/03/2026</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:08
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:41
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:25
-23/03/2024</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:36
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23:51
-23/03/2024</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+23/03/2026</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:52
-23/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">00:20
-24/03/2024</t>
+23/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1501,19 +1498,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>61</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1536,19 +1533,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>64</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>65</v>
       </c>
       <c r="F20" s="34">
         <v>-44.15</v>
@@ -1571,7 +1568,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1677,31 +1674,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1944,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1973,7 +1970,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1996,7 +1993,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
